--- a/光伏配储项目/电价数据/2026/盘允站.xlsx
+++ b/光伏配储项目/电价数据/2026/盘允站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5329199999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.18256</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6342100000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.96129</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.78413</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6953400000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43982</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42266</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.44844</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42246</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44537</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.70899</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.5773400000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.4626</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.25077</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.5086499999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.5344099999999999</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.23264</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.7315499999999999</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.73189</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.71841</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.43585</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.12793</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.26966</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.47867</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.74003</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.80583</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.27045</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.53779</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.59975</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.58648</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.7394400000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.68753</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.73175</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.27944</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.41376</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.60623</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.62862</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.11395</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.9165</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.7806799999999999</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.92427</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.10377</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.89789</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.58335</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.6458</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.32311</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.09991</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.66542</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.02043</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.15228</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.00879</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.33462</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.11654</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.11172</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.07137</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.69882</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47935</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42217</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.03729</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.93864</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.01101</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53611</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5352899999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49786</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.54334</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.73775</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72401</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45604</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44112</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.7924500000000001</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.92601</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.5640299999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.73078</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.78428</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.65947</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.60437</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.46937</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.48811</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.59215</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.9677</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.99621</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.27962</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.9265800000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.15818</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8206599999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.76516</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.15609</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.96469</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.8381000000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.33584</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.4719</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.56391</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.45821</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.05584</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.84765</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.8775599999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8012899999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7164299999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.73622</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.40233</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.8355399999999999</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.9975700000000001</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.99442</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.8131</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.20947</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.4321</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.36825</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.39773</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.47949</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.64764</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05376</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.15196</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.70901</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.86961</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.63427</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.6073500000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.76347</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33349</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51549</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.53486</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43364</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47334</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.59775</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.5972999999999999</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.73497</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.56309</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5789</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.46528</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.66998</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8449099999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.1674</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.57951</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.92249</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.21184</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.7495599999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.7867000000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.64608</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.75852</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.8717</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.43127</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.48475</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.85497</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.8072</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.8959600000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.38406</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.05721</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.0845</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.90263</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.84965</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.78955</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.17351</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.1891</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.08114</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.03615</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.02794</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.02926</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.97273</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.42527</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.86024</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.43102</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.85712</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8640599999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.94396</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.87326</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.97392</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.82175</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.64193</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.62917</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.48504</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.85462</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.56617</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.50337</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.5522400000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.53596</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46648</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5493300000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.51206</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.6164400000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.8352200000000001</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.88106</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.61918</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.93899</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.99452</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.58812</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.6776799999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.95069</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.89467</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.10119</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.79426</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.81151</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.50204</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.61126</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.46436</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.49846</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.76275</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.92301</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.7161799999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.7504299999999999</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.7950900000000001</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.73986</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.70953</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.67348</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.89501</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.55641</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.8667699999999999</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.8177000000000001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.59161</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.75313</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.7990499999999999</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.82075</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.89906</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9114099999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.89471</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.91104</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.4759</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.84538</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.8090900000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.8190499999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.84927</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.84665</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.81892</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.77154</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.57038</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3095</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.53054</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45165</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.18994</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.18533</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.21993</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.18561</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.25282</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.14724</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.18531</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.19924</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.14099</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.14174</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.24872</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.24117</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.26813</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.20672</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.18891</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.19028</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.18243</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.18247</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.13068</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.14605</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.16375</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.13857</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.26795</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.48198</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.48083</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31024</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.96608</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.7200299999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.75073</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5176799999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.5030899999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.20676</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06213</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.13721</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04437</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04188</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00279</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19148</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04238</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01901</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04231</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04236</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.13583</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04242</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.13641</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.1382</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.14672</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.15233</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.15279</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.15471</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33594</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.37814</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.24193</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.26604</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.5760599999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.6764199999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.5371699999999999</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.51048</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.5644199999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.60763</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.74188</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.47892</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.45524</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.6068300000000001</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.59927</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.69899</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.48418</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.39143</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14398</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.5656100000000001</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.5627799999999999</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.51964</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.51842</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48005</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.6430399999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79575</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7205199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.5228400000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.64738</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.92752</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.21815</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.7082000000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.23583</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.20674</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.6253</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.63146</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.19897</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.88326</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.57231</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.19481</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.60641</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.29123</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.6893400000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80457</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78759</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78838</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50592</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41634</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46454</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22344</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6392599999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5424099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50214</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42601</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45264</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40546</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59396</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43278</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5870700000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66484</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.76406</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.54696</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5584199999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.52904</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.22535</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.84017</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.10933</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.08735</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.05952</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.45551</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.61398</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.45541</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.50299</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.44455</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.63634</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.53023</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.46007</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.7436499999999999</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.62537</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.21808</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.50574</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.51651</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.41054</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.48139</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.50403</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.47981</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.47472</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.50046</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.49725</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.49091</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.51142</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.58584</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.50199</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.58092</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.51435</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.51006</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.52335</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.50408</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.49322</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.48868</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.43161</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.45939</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35309</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9557899999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54064</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.54061</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.55784</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.65188</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.7899700000000001</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.6319600000000001</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.73238</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.62737</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.6965399999999999</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.63714</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.5145700000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.72464</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.6572899999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.02156</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.6722100000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.54473</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.8490599999999999</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.60349</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.6138400000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.04659</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.57335</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.4362</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.7807799999999999</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.04856</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.6815</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.33358</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70355</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7952899999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64975</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.67552</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.40858</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.59484</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.57762</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.81796</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.6763400000000001</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.51174</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.98933</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.53843</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.99494</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.31303</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.05008</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.66449</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.46493</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.09731</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.97529</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.76673</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.75062</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.72461</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.7846000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.13998</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.95652</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.6139600000000001</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.93623</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.5541799999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.75464</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.7308</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.63822</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.67592</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.65967</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.78854</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.79657</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.6575599999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.8073899999999999</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.04742</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.74237</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.73639</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.8184900000000001</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.7029</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.72168</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.02433</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.71762</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.72605</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.7920900000000001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.68059</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.66822</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.23311</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.83814</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.38607</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.13331</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.75501</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.75293</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.6151</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3247</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43025</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24944</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.25825</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.65387</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23175</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.24675</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.27841</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.26957</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25117</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.51947</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44915</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54231</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46867</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.55814</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.45746</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.45378</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.54201</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.71312</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.67413</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.55008</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.50587</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.5974700000000001</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.69331</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.68676</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.5623899999999999</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40536</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41862</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47152</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.52446</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.63802</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.64118</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.6299</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.63227</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.89006</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.88393</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.57536</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.68732</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.03538</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.61425</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.01956</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.89962</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.89235</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.95973</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.71146</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.08616</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.69699</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.68529</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.62314</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.8919400000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.90843</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.92177</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.91689</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.8940499999999999</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.9185</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.72082</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.95164</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.12346</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.0369</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.9485800000000001</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.95631</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.9643999999999999</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.90591</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.9986799999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.62207</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.67296</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.9424</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.95077</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.94468</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.3962</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.02408</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.34084</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.97429</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.09387</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.56276</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.48635</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.77318</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.47318</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.65249</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31876</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.67461</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.59984</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.51983</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.59172</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.8303200000000001</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.7162500000000001</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.59069</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.5182</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.51873</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.95826</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56272</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40766</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.5142100000000001</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42979</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6519299999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83088</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.5375800000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.51194</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.6183200000000001</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.14909</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.22998</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.25233</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.49002</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.39311</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.67462</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.5955199999999999</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.90246</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.7400399999999999</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.21592</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.58882</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.7400099999999999</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.54023</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.7711399999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.7204199999999999</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.57162</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.16118</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6795099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.8583200000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5092</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.95374</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.25294</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.55262</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.86436</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.02001</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.8376699999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.63447</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.07253</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.89635</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.59889</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56043</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45059</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.04684</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.55869</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.63085</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.36104</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.31901</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.48664</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.7796</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.76969</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.78428</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.36677</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.39765</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.52811</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7057</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.6678999999999999</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.73765</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.23331</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.69151</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.52771</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.26804</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.20825</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.12785</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.05989</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.7528400000000001</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.68857</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.00883</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.48045</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.49556</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.60577</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.8383400000000001</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.57204</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.72373</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.5561900000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.74113</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.7422300000000001</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.16716</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.12449</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.86929</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.8704299999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.9858899999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.00002</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.34299</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.60796</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.43527</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.04907</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.14514</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.78338</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.6346</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.6144</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.88493</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.78042</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47806</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47144</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.9805900000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6028600000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.42618</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.48489</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.44538</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.5755</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.55147</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.55524</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.86733</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.8127300000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.13569</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.06148</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.71457</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7252799999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.51993</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.46277</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.46525</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42639</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.49352</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.52979</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.61281</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.77395</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.5135</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.16369</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.24914</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.15903</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24058</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.25326</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.17409</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.2028</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.23016</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.50314</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.42114</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.48093</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44193</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43869</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35168</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.5538500000000001</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19652</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.21478</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.20634</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.16501</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.14985</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.24163</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.14872</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.16329</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.14457</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.19514</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.46103</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.19621</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.14823</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.18935</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.14005</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.15849</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.14652</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.14027</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.16481</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.13927</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.14667</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.13929</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.14965</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.14761</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.14774</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.18429</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.26032</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.60361</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2871</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.78179</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.7539600000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.50731</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.57698</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.5167200000000001</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.8612300000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8642300000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.9809600000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.82704</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.62849</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.86393</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25383</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.01798</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.20041</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.14294</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.15446</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.6143999999999999</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.46511</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.42276</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.71216</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.26517</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.57525</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.51189</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.85995</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.6859</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.68833</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.69498</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.7017599999999999</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.82109</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7310800000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.5586599999999999</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.7566799999999999</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.79955</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.12548</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.12446</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.16049</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.51848</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.12594</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.21133</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.27728</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.60943</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8620800000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7323099999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.78059</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.77839</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.05613</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.91223</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7178600000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33589</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.60219</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.45405</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.56111</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.56189</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.24294</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.87276</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.7163999999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.64797</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.6030599999999999</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49157</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.56731</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.49183</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.7131799999999999</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.8502799999999999</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.76281</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.85311</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.15055</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.14521</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.7739</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.79174</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.5688200000000001</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.43838</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.44035</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.49055</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.50197</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.97712</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.62429</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.43775</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.41178</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.45971</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.46482</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.44674</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.46556</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.5274099999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.82821</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.78853</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.52698</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.6522899999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.56459</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.82862</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.68857</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.45555</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.44335</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33804</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.5135599999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58456</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.5360900000000001</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.7750900000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.01308</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.36144</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.58748</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.72319</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.72946</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.76803</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.7162000000000001</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.6889500000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.72277</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.7014600000000001</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.6906</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.69377</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.06259</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.68453</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.48523</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.69892</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.7054199999999999</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.50272</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.68725</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.5817100000000001</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.69926</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.6827000000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.7046699999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.9421499999999999</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.09225</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.11479</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.16209</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.22881</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.21188</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.28171</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.29416</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.27205</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.92711</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.82176</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.78823</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47812</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.98233</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.75783</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.84089</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.7201799999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.66983</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.65503</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.6531399999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.62827</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6849700000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.54135</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.5565099999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.62118</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.58596</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.66072</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.44821</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.67987</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.5634199999999999</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.68525</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.62034</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.62305</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.5355800000000001</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.46004</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.48644</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.77079</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.62005</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.76985</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.6998099999999999</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.77789</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.76067</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.7607999999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.99597</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.01487</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.7376200000000001</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.5557000000000001</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5850599999999999</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.66396</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.6475599999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.66999</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.10464</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.10679</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.41853</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.12765</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.42218</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.40381</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.43578</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.23304</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.15766</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.85624</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.83678</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.46476</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.53822</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.2616</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.26284</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.08522</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.45244</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.54312</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.51907</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.02203</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.96199</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.72376</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.23176</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.21007</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.48662</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.25348</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.25526</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.63506</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.61663</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.59965</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37506</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.55987</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.43486</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.5425800000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.7996599999999999</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.5788</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.60519</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.78095</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.93736</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.5093</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.25397</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.98068</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.9272999999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.58339</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.40329</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.13628</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.4963399999999999</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.23932</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15062</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.5767100000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.20242</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.57965</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.6691900000000001</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.5699500000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.67443</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.48932</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.78498</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.6435599999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.5366799999999999</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.69637</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.56701</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.6988799999999999</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.78277</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.83749</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.7024900000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.71384</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.68516</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.69532</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.7059299999999999</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.07711</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.12405</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.01351</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.03261</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.19749</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.96453</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.9911599999999999</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.76464</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.74507</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.75918</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.79701</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.7952400000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.77658</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.8879199999999999</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.59346</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.57289</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.51859</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.49923</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37533</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.25271</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.83774</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.8691</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.10324</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.71294</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44082</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.59296</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.48306</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.5659299999999999</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.53234</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.66432</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.56716</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.66983</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.15043</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.69616</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.75429</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.8483999999999999</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.83701</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.73781</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.94359</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.70577</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.07561</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.7040299999999999</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.47587</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.57192</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.72151</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.56099</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.03095</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8314199999999999</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.5502400000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.19209</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.7743</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.77735</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.23364</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.19759</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.01382</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.83905</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.79855</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.81151</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.8117000000000001</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.83892</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.83624</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.8623500000000001</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.22341</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.26077</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.34512</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.69211</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.79015</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.8127799999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.7883600000000001</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.83536</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.48197</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.7432</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.9731300000000001</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.5672699999999999</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.46898</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.92528</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.6041799999999999</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.60612</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.45651</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.44265</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.43437</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.65395</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.5146900000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.74779</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.9970599999999999</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.7142500000000001</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.7450399999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.46301</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.37089</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.91959</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.59294</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.52913</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.45807</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.60085</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.48622</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.78884</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.65826</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.66761</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.69625</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.7191000000000001</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.5420700000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.52201</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.51014</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.52273</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.5286799999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.54462</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.60715</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.61415</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.51622</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.60439</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6145700000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.87482</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.64724</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.56425</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.56211</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.5464600000000001</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5112099999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.64151</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.62303</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.6604800000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.54804</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.51295</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.44808</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
